--- a/forms/trg/Formulir_TRG_respobio.xlsx
+++ b/forms/trg/Formulir_TRG_respobio.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B22)</f>
+        <f>COUNTA(Anggota!B5:B23)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F22)</f>
+        <f>COUNTA(Anggota!F5:F23)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,27 +913,31 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Naurah Nazifah Sarmadi</t>
+          <t>Muspirah Djalal, M.Sc</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="12" t="n"/>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>Graduate Student</t>
-        </is>
-      </c>
+      <c r="E5" s="11" t="n"/>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="12" t="n"/>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>5976161</t>
+        </is>
+      </c>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>57212143330</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -946,12 +950,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Shabrina Nuramadhani</t>
+          <t>Naurah Nazifah Sarmadi</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D6" s="12" t="n"/>
@@ -979,22 +983,18 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Rafiqa Awalina Putri</t>
+          <t>Shabrina Nuramadhani</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>Magister Student</t>
-        </is>
-      </c>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n"/>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Technology in food</t>
+          <t>Graduate Student</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Cinta Aulia Putri</t>
+          <t>Rafiqa Awalina Putri</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Abel Yandi Novrain</t>
+          <t>Cinta Aulia Putri</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Smart Packaging</t>
+          <t>Technology in food</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Ainun</t>
+          <t>Abel Yandi Novrain</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Post-harvest Technology</t>
+          <t>Smart Packaging</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1125,10 +1125,26 @@
       <c r="A11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="11" t="n"/>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Ainun</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Magister Student</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Post-harvest Technology</t>
+        </is>
+      </c>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
@@ -1136,7 +1152,11 @@
       <c r="J11" s="12" t="n"/>
       <c r="K11" s="12" t="n"/>
       <c r="L11" s="12" t="n"/>
-      <c r="M11" s="12" t="n"/>
+      <c r="M11" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -1325,15 +1345,32 @@
       <c r="L22" s="12" t="n"/>
       <c r="M22" s="12" t="n"/>
     </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="12" t="n"/>
+      <c r="C23" s="12" t="n"/>
+      <c r="D23" s="12" t="n"/>
+      <c r="E23" s="11" t="n"/>
+      <c r="F23" s="12" t="n"/>
+      <c r="G23" s="12" t="n"/>
+      <c r="H23" s="12" t="n"/>
+      <c r="I23" s="12" t="n"/>
+      <c r="J23" s="12" t="n"/>
+      <c r="K23" s="12" t="n"/>
+      <c r="L23" s="12" t="n"/>
+      <c r="M23" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
